--- a/nriss-patch-2/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,7 +781,7 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260916095457</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -1157,7 +1157,7 @@
     <t>A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260916095455</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -6424,7 +6424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>312</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>79</v>
